--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90EFC67D-2C3E-43FE-91BC-285FB4759C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65078D8D-72CE-4BDA-A3A7-A2D46B163403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC8D33D-1633-4161-A340-1CF10F4E980F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED62563-5BC4-4CDA-AD82-DCAFE347069A}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65078D8D-72CE-4BDA-A3A7-A2D46B163403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{734E40DC-C11F-4623-9816-68F8602BC9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED62563-5BC4-4CDA-AD82-DCAFE347069A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5568741B-D9B3-45DD-AC37-E8B716A56AD8}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{734E40DC-C11F-4623-9816-68F8602BC9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60331D57-468D-4F64-85AA-10DF3A049545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5568741B-D9B3-45DD-AC37-E8B716A56AD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92069626-B2C5-4DA4-A4A9-80786C52C8D6}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60331D57-468D-4F64-85AA-10DF3A049545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0291BA7-BA37-4544-B6D8-5C22DA9E7D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92069626-B2C5-4DA4-A4A9-80786C52C8D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B2EC5F-363A-4447-BCC7-30982B4C8AFF}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0291BA7-BA37-4544-B6D8-5C22DA9E7D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D3C7E87-3460-42D6-928C-97531BD72422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B2EC5F-363A-4447-BCC7-30982B4C8AFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{541FD66C-E2B8-4398-B782-3ACEC013390A}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D3C7E87-3460-42D6-928C-97531BD72422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B1CBA3E-0D18-4695-8468-F83D0232CCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{541FD66C-E2B8-4398-B782-3ACEC013390A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB51DC59-6418-48C9-9555-5549D3B3E359}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B1CBA3E-0D18-4695-8468-F83D0232CCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA8C6A4A-77FD-45A3-9A71-3B8F441CA274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB51DC59-6418-48C9-9555-5549D3B3E359}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F966AD-B214-44F6-B0B8-55DE4FECF54E}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA8C6A4A-77FD-45A3-9A71-3B8F441CA274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66023C7-B104-413A-88D1-EA4818CE7E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F966AD-B214-44F6-B0B8-55DE4FECF54E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D0104D-ED41-4D94-BED8-3677A351D2C6}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66023C7-B104-413A-88D1-EA4818CE7E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03C73B15-89D7-40A0-9665-A418B79FE79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D0104D-ED41-4D94-BED8-3677A351D2C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F073DCD2-DC3E-45A3-BDEC-8234AC91C435}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03C73B15-89D7-40A0-9665-A418B79FE79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F434189-AE77-40EB-8682-23F986AA23ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F073DCD2-DC3E-45A3-BDEC-8234AC91C435}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A796DE02-F6B9-4321-9A76-F794ADE172C8}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F434189-AE77-40EB-8682-23F986AA23ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03DB9A9B-B2BC-4A17-AF2C-663C4A1A40BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A796DE02-F6B9-4321-9A76-F794ADE172C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C07D208-0F09-4D70-80C9-1FC654D0DF43}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03DB9A9B-B2BC-4A17-AF2C-663C4A1A40BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4ECF691-E777-449F-BB4E-A846300CB9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -7823,7 +7823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C07D208-0F09-4D70-80C9-1FC654D0DF43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD9B02F1-5E4A-4686-9910-DE48A2D80F82}">
   <dimension ref="B9:E1116"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A9237A9-BB0F-45CE-B01B-3A5BD696D931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B60E95B8-E10D-468E-97D6-08C2723B9FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{209A79C2-BD4E-4695-8B03-A696D55F3561}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88515D14-D5E2-495D-8FB7-BBB0BBEE0DED}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B60E95B8-E10D-468E-97D6-08C2723B9FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CBF06A8-35E2-473C-9BB7-C479EB63562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88515D14-D5E2-495D-8FB7-BBB0BBEE0DED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E66331F-B403-45CE-9F04-AEB2E9372FAC}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CBF06A8-35E2-473C-9BB7-C479EB63562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98AE71D0-1705-49CA-B4ED-1DE1CD0A231B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E66331F-B403-45CE-9F04-AEB2E9372FAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5BD233-2908-4E1E-8E90-83FC0561C450}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -5,16 +5,17 @@
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52485F27-B929-4917-B544-8B3D23B3A785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34DC064-9DBC-455F-947D-388AD39D7DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
-    <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId2"/>
+    <sheet name="geo_sets" sheetId="3" r:id="rId2"/>
+    <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="680">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -331,6 +332,1752 @@
   </si>
   <si>
     <t>distr*</t>
+  </si>
+  <si>
+    <t>~tfm_psets</t>
+  </si>
+  <si>
+    <t>setname</t>
+  </si>
+  <si>
+    <t>pset_co</t>
+  </si>
+  <si>
+    <t>pset_ci</t>
+  </si>
+  <si>
+    <t>t_pos_andor</t>
+  </si>
+  <si>
+    <t>p_w66098469</t>
+  </si>
+  <si>
+    <t>e_w66098469*</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>p_w87538349</t>
+  </si>
+  <si>
+    <t>e_w87538349*</t>
+  </si>
+  <si>
+    <t>p_w102958903</t>
+  </si>
+  <si>
+    <t>e_w102958903*</t>
+  </si>
+  <si>
+    <t>p_w104173570</t>
+  </si>
+  <si>
+    <t>e_w104173570*</t>
+  </si>
+  <si>
+    <t>p_w104391636</t>
+  </si>
+  <si>
+    <t>e_w104391636*</t>
+  </si>
+  <si>
+    <t>p_w104530060</t>
+  </si>
+  <si>
+    <t>e_w104530060*</t>
+  </si>
+  <si>
+    <t>p_w105298089</t>
+  </si>
+  <si>
+    <t>e_w105298089*</t>
+  </si>
+  <si>
+    <t>p_w106076988</t>
+  </si>
+  <si>
+    <t>e_w106076988*</t>
+  </si>
+  <si>
+    <t>p_w106309481</t>
+  </si>
+  <si>
+    <t>e_w106309481*</t>
+  </si>
+  <si>
+    <t>p_w109834508</t>
+  </si>
+  <si>
+    <t>e_w109834508*</t>
+  </si>
+  <si>
+    <t>p_w109850439</t>
+  </si>
+  <si>
+    <t>e_w109850439*</t>
+  </si>
+  <si>
+    <t>p_w110682956</t>
+  </si>
+  <si>
+    <t>e_w110682956*</t>
+  </si>
+  <si>
+    <t>p_w116559939</t>
+  </si>
+  <si>
+    <t>e_w116559939*</t>
+  </si>
+  <si>
+    <t>p_w128581912</t>
+  </si>
+  <si>
+    <t>e_w128581912*</t>
+  </si>
+  <si>
+    <t>p_w132913106</t>
+  </si>
+  <si>
+    <t>e_w132913106*</t>
+  </si>
+  <si>
+    <t>p_w133641619</t>
+  </si>
+  <si>
+    <t>e_w133641619*</t>
+  </si>
+  <si>
+    <t>p_w133644487</t>
+  </si>
+  <si>
+    <t>e_w133644487*</t>
+  </si>
+  <si>
+    <t>p_w142662111</t>
+  </si>
+  <si>
+    <t>e_w142662111*</t>
+  </si>
+  <si>
+    <t>p_w145079972</t>
+  </si>
+  <si>
+    <t>e_w145079972*</t>
+  </si>
+  <si>
+    <t>p_w149843487</t>
+  </si>
+  <si>
+    <t>e_w149843487*</t>
+  </si>
+  <si>
+    <t>p_w150035494</t>
+  </si>
+  <si>
+    <t>e_w150035494*</t>
+  </si>
+  <si>
+    <t>p_w150065045</t>
+  </si>
+  <si>
+    <t>e_w150065045*</t>
+  </si>
+  <si>
+    <t>p_w151379730</t>
+  </si>
+  <si>
+    <t>e_w151379730*</t>
+  </si>
+  <si>
+    <t>p_w156208858</t>
+  </si>
+  <si>
+    <t>e_w156208858*</t>
+  </si>
+  <si>
+    <t>p_w161727149</t>
+  </si>
+  <si>
+    <t>e_w161727149*</t>
+  </si>
+  <si>
+    <t>p_w161870227</t>
+  </si>
+  <si>
+    <t>e_w161870227*</t>
+  </si>
+  <si>
+    <t>p_w161946849</t>
+  </si>
+  <si>
+    <t>e_w161946849*</t>
+  </si>
+  <si>
+    <t>p_w168727982</t>
+  </si>
+  <si>
+    <t>e_w168727982*</t>
+  </si>
+  <si>
+    <t>p_w168839127</t>
+  </si>
+  <si>
+    <t>e_w168839127*</t>
+  </si>
+  <si>
+    <t>p_w168857610</t>
+  </si>
+  <si>
+    <t>e_w168857610*</t>
+  </si>
+  <si>
+    <t>p_w169031921</t>
+  </si>
+  <si>
+    <t>e_w169031921*</t>
+  </si>
+  <si>
+    <t>p_w169031998</t>
+  </si>
+  <si>
+    <t>e_w169031998*</t>
+  </si>
+  <si>
+    <t>p_w169122898</t>
+  </si>
+  <si>
+    <t>e_w169122898*</t>
+  </si>
+  <si>
+    <t>p_w169249243</t>
+  </si>
+  <si>
+    <t>e_w169249243*</t>
+  </si>
+  <si>
+    <t>p_w256682313</t>
+  </si>
+  <si>
+    <t>e_w256682313*</t>
+  </si>
+  <si>
+    <t>p_w169359724</t>
+  </si>
+  <si>
+    <t>e_w169359724*</t>
+  </si>
+  <si>
+    <t>p_w169963227</t>
+  </si>
+  <si>
+    <t>e_w169963227*</t>
+  </si>
+  <si>
+    <t>p_w170247312</t>
+  </si>
+  <si>
+    <t>e_w170247312*</t>
+  </si>
+  <si>
+    <t>p_w170366035</t>
+  </si>
+  <si>
+    <t>e_w170366035*</t>
+  </si>
+  <si>
+    <t>p_w170537514</t>
+  </si>
+  <si>
+    <t>e_w170537514*</t>
+  </si>
+  <si>
+    <t>p_w170568495</t>
+  </si>
+  <si>
+    <t>e_w170568495*</t>
+  </si>
+  <si>
+    <t>p_w170589736</t>
+  </si>
+  <si>
+    <t>e_w170589736*</t>
+  </si>
+  <si>
+    <t>p_w170605907</t>
+  </si>
+  <si>
+    <t>e_w170605907*</t>
+  </si>
+  <si>
+    <t>p_w170850727</t>
+  </si>
+  <si>
+    <t>e_w170850727*</t>
+  </si>
+  <si>
+    <t>p_w170974371</t>
+  </si>
+  <si>
+    <t>e_w170974371*</t>
+  </si>
+  <si>
+    <t>p_w171066843</t>
+  </si>
+  <si>
+    <t>e_w171066843*</t>
+  </si>
+  <si>
+    <t>p_w172144358</t>
+  </si>
+  <si>
+    <t>e_w172144358*</t>
+  </si>
+  <si>
+    <t>p_w172601929</t>
+  </si>
+  <si>
+    <t>e_w172601929*</t>
+  </si>
+  <si>
+    <t>p_w172907196</t>
+  </si>
+  <si>
+    <t>e_w172907196*</t>
+  </si>
+  <si>
+    <t>p_w174636874</t>
+  </si>
+  <si>
+    <t>e_w174636874*</t>
+  </si>
+  <si>
+    <t>p_w185029969</t>
+  </si>
+  <si>
+    <t>e_w185029969*</t>
+  </si>
+  <si>
+    <t>p_w186510275</t>
+  </si>
+  <si>
+    <t>e_w186510275*</t>
+  </si>
+  <si>
+    <t>p_w187988970</t>
+  </si>
+  <si>
+    <t>e_w187988970*</t>
+  </si>
+  <si>
+    <t>p_w190769051</t>
+  </si>
+  <si>
+    <t>e_w190769051*</t>
+  </si>
+  <si>
+    <t>p_w193544791</t>
+  </si>
+  <si>
+    <t>e_w193544791*</t>
+  </si>
+  <si>
+    <t>p_w195615141</t>
+  </si>
+  <si>
+    <t>e_w195615141*</t>
+  </si>
+  <si>
+    <t>p_w201293312</t>
+  </si>
+  <si>
+    <t>e_w201293312*</t>
+  </si>
+  <si>
+    <t>p_w204258596</t>
+  </si>
+  <si>
+    <t>e_w204258596*</t>
+  </si>
+  <si>
+    <t>p_w209429410</t>
+  </si>
+  <si>
+    <t>e_w209429410*</t>
+  </si>
+  <si>
+    <t>p_w209726348</t>
+  </si>
+  <si>
+    <t>e_w209726348*</t>
+  </si>
+  <si>
+    <t>p_w210090094</t>
+  </si>
+  <si>
+    <t>e_w210090094*</t>
+  </si>
+  <si>
+    <t>p_w211412000</t>
+  </si>
+  <si>
+    <t>e_w211412000*</t>
+  </si>
+  <si>
+    <t>p_w215451416</t>
+  </si>
+  <si>
+    <t>e_w215451416*</t>
+  </si>
+  <si>
+    <t>p_w216502300</t>
+  </si>
+  <si>
+    <t>e_w216502300*</t>
+  </si>
+  <si>
+    <t>p_w216778426</t>
+  </si>
+  <si>
+    <t>e_w216778426*</t>
+  </si>
+  <si>
+    <t>p_w216953915</t>
+  </si>
+  <si>
+    <t>e_w216953915*</t>
+  </si>
+  <si>
+    <t>p_w216956620</t>
+  </si>
+  <si>
+    <t>e_w216956620*</t>
+  </si>
+  <si>
+    <t>p_w241822621</t>
+  </si>
+  <si>
+    <t>e_w241822621*</t>
+  </si>
+  <si>
+    <t>p_w241822623</t>
+  </si>
+  <si>
+    <t>e_w241822623*</t>
+  </si>
+  <si>
+    <t>p_w241822631</t>
+  </si>
+  <si>
+    <t>e_w241822631*</t>
+  </si>
+  <si>
+    <t>p_w241828221</t>
+  </si>
+  <si>
+    <t>e_w241828221*</t>
+  </si>
+  <si>
+    <t>p_w242103481</t>
+  </si>
+  <si>
+    <t>e_w242103481*</t>
+  </si>
+  <si>
+    <t>p_w242103532</t>
+  </si>
+  <si>
+    <t>e_w242103532*</t>
+  </si>
+  <si>
+    <t>p_w242253500</t>
+  </si>
+  <si>
+    <t>e_w242253500*</t>
+  </si>
+  <si>
+    <t>p_w250540807</t>
+  </si>
+  <si>
+    <t>e_w250540807*</t>
+  </si>
+  <si>
+    <t>p_w253566674</t>
+  </si>
+  <si>
+    <t>e_w253566674*</t>
+  </si>
+  <si>
+    <t>p_w291678103</t>
+  </si>
+  <si>
+    <t>e_w291678103*</t>
+  </si>
+  <si>
+    <t>p_w307942220</t>
+  </si>
+  <si>
+    <t>e_w307942220*</t>
+  </si>
+  <si>
+    <t>p_w315434358</t>
+  </si>
+  <si>
+    <t>e_w315434358*</t>
+  </si>
+  <si>
+    <t>p_w315461259</t>
+  </si>
+  <si>
+    <t>e_w315461259*</t>
+  </si>
+  <si>
+    <t>p_w315461272</t>
+  </si>
+  <si>
+    <t>e_w315461272*</t>
+  </si>
+  <si>
+    <t>p_w315618377</t>
+  </si>
+  <si>
+    <t>e_w315618377*</t>
+  </si>
+  <si>
+    <t>p_w315662839</t>
+  </si>
+  <si>
+    <t>e_w315662839*</t>
+  </si>
+  <si>
+    <t>p_w317416612</t>
+  </si>
+  <si>
+    <t>e_w317416612*</t>
+  </si>
+  <si>
+    <t>p_w317511904</t>
+  </si>
+  <si>
+    <t>e_w317511904*</t>
+  </si>
+  <si>
+    <t>p_w320438391</t>
+  </si>
+  <si>
+    <t>e_w320438391*</t>
+  </si>
+  <si>
+    <t>p_w405626236</t>
+  </si>
+  <si>
+    <t>e_w405626236*</t>
+  </si>
+  <si>
+    <t>p_w421647841</t>
+  </si>
+  <si>
+    <t>e_w421647841*</t>
+  </si>
+  <si>
+    <t>p_w459476442</t>
+  </si>
+  <si>
+    <t>e_w459476442*</t>
+  </si>
+  <si>
+    <t>p_w505170104</t>
+  </si>
+  <si>
+    <t>e_w505170104*</t>
+  </si>
+  <si>
+    <t>p_w659138214</t>
+  </si>
+  <si>
+    <t>e_w659138214*</t>
+  </si>
+  <si>
+    <t>p_w714627759</t>
+  </si>
+  <si>
+    <t>e_w714627759*</t>
+  </si>
+  <si>
+    <t>p_w722673849</t>
+  </si>
+  <si>
+    <t>e_w722673849*</t>
+  </si>
+  <si>
+    <t>p_w785319805</t>
+  </si>
+  <si>
+    <t>e_w785319805*</t>
+  </si>
+  <si>
+    <t>p_w832823487</t>
+  </si>
+  <si>
+    <t>e_w832823487*</t>
+  </si>
+  <si>
+    <t>p_w901872431</t>
+  </si>
+  <si>
+    <t>e_w901872431*</t>
+  </si>
+  <si>
+    <t>p_w901872439</t>
+  </si>
+  <si>
+    <t>e_w901872439*</t>
+  </si>
+  <si>
+    <t>p_w1029010255</t>
+  </si>
+  <si>
+    <t>e_w1029010255*</t>
+  </si>
+  <si>
+    <t>p_w975217734</t>
+  </si>
+  <si>
+    <t>e_w975217734*</t>
+  </si>
+  <si>
+    <t>p_w1028554758</t>
+  </si>
+  <si>
+    <t>e_w1028554758*</t>
+  </si>
+  <si>
+    <t>p_w1030329139</t>
+  </si>
+  <si>
+    <t>e_w1030329139*</t>
+  </si>
+  <si>
+    <t>p_w1037299172</t>
+  </si>
+  <si>
+    <t>e_w1037299172*</t>
+  </si>
+  <si>
+    <t>p_w1037516198</t>
+  </si>
+  <si>
+    <t>e_w1037516198*</t>
+  </si>
+  <si>
+    <t>p_w1038584990</t>
+  </si>
+  <si>
+    <t>e_w1038584990*</t>
+  </si>
+  <si>
+    <t>p_r2269992</t>
+  </si>
+  <si>
+    <t>e_r2269992*</t>
+  </si>
+  <si>
+    <t>p_r11529219</t>
+  </si>
+  <si>
+    <t>e_r11529219*</t>
+  </si>
+  <si>
+    <t>p_r11529637</t>
+  </si>
+  <si>
+    <t>e_r11529637*</t>
+  </si>
+  <si>
+    <t>p_r13768299</t>
+  </si>
+  <si>
+    <t>e_r13768299*</t>
+  </si>
+  <si>
+    <t>p_r15580570</t>
+  </si>
+  <si>
+    <t>e_r15580570*</t>
+  </si>
+  <si>
+    <t>p_r17013811</t>
+  </si>
+  <si>
+    <t>e_r17013811*</t>
+  </si>
+  <si>
+    <t>p_JP21</t>
+  </si>
+  <si>
+    <t>e_JP21*</t>
+  </si>
+  <si>
+    <t>p_JP36</t>
+  </si>
+  <si>
+    <t>e_JP36*</t>
+  </si>
+  <si>
+    <t>p_JP28</t>
+  </si>
+  <si>
+    <t>e_JP28*</t>
+  </si>
+  <si>
+    <t>p_JP60</t>
+  </si>
+  <si>
+    <t>e_JP60*</t>
+  </si>
+  <si>
+    <t>p_JP23</t>
+  </si>
+  <si>
+    <t>e_JP23*</t>
+  </si>
+  <si>
+    <t>p_JP95</t>
+  </si>
+  <si>
+    <t>e_JP95*</t>
+  </si>
+  <si>
+    <t>p_JP191</t>
+  </si>
+  <si>
+    <t>e_JP191*</t>
+  </si>
+  <si>
+    <t>p_JP116</t>
+  </si>
+  <si>
+    <t>e_JP116*</t>
+  </si>
+  <si>
+    <t>p_JP156</t>
+  </si>
+  <si>
+    <t>e_JP156*</t>
+  </si>
+  <si>
+    <t>p_JP141</t>
+  </si>
+  <si>
+    <t>e_JP141*</t>
+  </si>
+  <si>
+    <t>p_JP122</t>
+  </si>
+  <si>
+    <t>e_JP122*</t>
+  </si>
+  <si>
+    <t>p_JP178</t>
+  </si>
+  <si>
+    <t>e_JP178*</t>
+  </si>
+  <si>
+    <t>p_JP117</t>
+  </si>
+  <si>
+    <t>e_JP117*</t>
+  </si>
+  <si>
+    <t>p_JP132</t>
+  </si>
+  <si>
+    <t>e_JP132*</t>
+  </si>
+  <si>
+    <t>p_JP269</t>
+  </si>
+  <si>
+    <t>e_JP269*</t>
+  </si>
+  <si>
+    <t>p_JP19</t>
+  </si>
+  <si>
+    <t>e_JP19*</t>
+  </si>
+  <si>
+    <t>p_JP267</t>
+  </si>
+  <si>
+    <t>e_JP267*</t>
+  </si>
+  <si>
+    <t>p_JP102</t>
+  </si>
+  <si>
+    <t>e_JP102*</t>
+  </si>
+  <si>
+    <t>p_JP112</t>
+  </si>
+  <si>
+    <t>e_JP112*</t>
+  </si>
+  <si>
+    <t>p_JP106</t>
+  </si>
+  <si>
+    <t>e_JP106*</t>
+  </si>
+  <si>
+    <t>p_JP96</t>
+  </si>
+  <si>
+    <t>e_JP96*</t>
+  </si>
+  <si>
+    <t>p_JP9</t>
+  </si>
+  <si>
+    <t>e_JP9*</t>
+  </si>
+  <si>
+    <t>p_JP292</t>
+  </si>
+  <si>
+    <t>e_JP292*</t>
+  </si>
+  <si>
+    <t>p_JP294</t>
+  </si>
+  <si>
+    <t>e_JP294*</t>
+  </si>
+  <si>
+    <t>p_JP41</t>
+  </si>
+  <si>
+    <t>e_JP41*</t>
+  </si>
+  <si>
+    <t>p_JP29</t>
+  </si>
+  <si>
+    <t>e_JP29*</t>
+  </si>
+  <si>
+    <t>p_JP37</t>
+  </si>
+  <si>
+    <t>e_JP37*</t>
+  </si>
+  <si>
+    <t>p_JP218</t>
+  </si>
+  <si>
+    <t>e_JP218*</t>
+  </si>
+  <si>
+    <t>p_w242253537</t>
+  </si>
+  <si>
+    <t>e_w242253537*</t>
+  </si>
+  <si>
+    <t>p_JP10</t>
+  </si>
+  <si>
+    <t>e_JP10*</t>
+  </si>
+  <si>
+    <t>p_JP57</t>
+  </si>
+  <si>
+    <t>e_JP57*</t>
+  </si>
+  <si>
+    <t>p_JP30</t>
+  </si>
+  <si>
+    <t>e_JP30*</t>
+  </si>
+  <si>
+    <t>p_JP34</t>
+  </si>
+  <si>
+    <t>e_JP34*</t>
+  </si>
+  <si>
+    <t>p_JP118</t>
+  </si>
+  <si>
+    <t>e_JP118*</t>
+  </si>
+  <si>
+    <t>p_JP119</t>
+  </si>
+  <si>
+    <t>e_JP119*</t>
+  </si>
+  <si>
+    <t>p_JP135</t>
+  </si>
+  <si>
+    <t>e_JP135*</t>
+  </si>
+  <si>
+    <t>p_JP158</t>
+  </si>
+  <si>
+    <t>e_JP158*</t>
+  </si>
+  <si>
+    <t>p_JP121</t>
+  </si>
+  <si>
+    <t>e_JP121*</t>
+  </si>
+  <si>
+    <t>p_JP124</t>
+  </si>
+  <si>
+    <t>e_JP124*</t>
+  </si>
+  <si>
+    <t>p_JP248</t>
+  </si>
+  <si>
+    <t>e_JP248*</t>
+  </si>
+  <si>
+    <t>p_JP76</t>
+  </si>
+  <si>
+    <t>e_JP76*</t>
+  </si>
+  <si>
+    <t>p_JP155</t>
+  </si>
+  <si>
+    <t>e_JP155*</t>
+  </si>
+  <si>
+    <t>p_JP219</t>
+  </si>
+  <si>
+    <t>e_JP219*</t>
+  </si>
+  <si>
+    <t>p_JP296</t>
+  </si>
+  <si>
+    <t>e_JP296*</t>
+  </si>
+  <si>
+    <t>p_JP74</t>
+  </si>
+  <si>
+    <t>e_JP74*</t>
+  </si>
+  <si>
+    <t>p_JP137</t>
+  </si>
+  <si>
+    <t>e_JP137*</t>
+  </si>
+  <si>
+    <t>p_JP50</t>
+  </si>
+  <si>
+    <t>e_JP50*</t>
+  </si>
+  <si>
+    <t>p_JP49</t>
+  </si>
+  <si>
+    <t>e_JP49*</t>
+  </si>
+  <si>
+    <t>p_JP249</t>
+  </si>
+  <si>
+    <t>e_JP249*</t>
+  </si>
+  <si>
+    <t>p_JP175</t>
+  </si>
+  <si>
+    <t>e_JP175*</t>
+  </si>
+  <si>
+    <t>p_JP306</t>
+  </si>
+  <si>
+    <t>e_JP306*</t>
+  </si>
+  <si>
+    <t>p_JP25</t>
+  </si>
+  <si>
+    <t>e_JP25*</t>
+  </si>
+  <si>
+    <t>p_JP101</t>
+  </si>
+  <si>
+    <t>e_JP101*</t>
+  </si>
+  <si>
+    <t>p_JP100</t>
+  </si>
+  <si>
+    <t>e_JP100*</t>
+  </si>
+  <si>
+    <t>p_JP103</t>
+  </si>
+  <si>
+    <t>e_JP103*</t>
+  </si>
+  <si>
+    <t>p_JP111</t>
+  </si>
+  <si>
+    <t>e_JP111*</t>
+  </si>
+  <si>
+    <t>p_JP109</t>
+  </si>
+  <si>
+    <t>e_JP109*</t>
+  </si>
+  <si>
+    <t>p_JP108</t>
+  </si>
+  <si>
+    <t>e_JP108*</t>
+  </si>
+  <si>
+    <t>p_JP107</t>
+  </si>
+  <si>
+    <t>e_JP107*</t>
+  </si>
+  <si>
+    <t>p_JP110</t>
+  </si>
+  <si>
+    <t>e_JP110*</t>
+  </si>
+  <si>
+    <t>p_JP120</t>
+  </si>
+  <si>
+    <t>e_JP120*</t>
+  </si>
+  <si>
+    <t>p_JP73</t>
+  </si>
+  <si>
+    <t>e_JP73*</t>
+  </si>
+  <si>
+    <t>p_w179863079</t>
+  </si>
+  <si>
+    <t>e_w179863079*</t>
+  </si>
+  <si>
+    <t>p_w801582512</t>
+  </si>
+  <si>
+    <t>e_w801582512*</t>
+  </si>
+  <si>
+    <t>p_JP5</t>
+  </si>
+  <si>
+    <t>e_JP5*</t>
+  </si>
+  <si>
+    <t>p_JP1</t>
+  </si>
+  <si>
+    <t>e_JP1*</t>
+  </si>
+  <si>
+    <t>p_JP2</t>
+  </si>
+  <si>
+    <t>e_JP2*</t>
+  </si>
+  <si>
+    <t>p_JP8</t>
+  </si>
+  <si>
+    <t>e_JP8*</t>
+  </si>
+  <si>
+    <t>p_JP7</t>
+  </si>
+  <si>
+    <t>e_JP7*</t>
+  </si>
+  <si>
+    <t>p_JP6</t>
+  </si>
+  <si>
+    <t>e_JP6*</t>
+  </si>
+  <si>
+    <t>p_JP4</t>
+  </si>
+  <si>
+    <t>e_JP4*</t>
+  </si>
+  <si>
+    <t>p_JP3</t>
+  </si>
+  <si>
+    <t>e_JP3*</t>
+  </si>
+  <si>
+    <t>rez_spv_001</t>
+  </si>
+  <si>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>rez_spv_002</t>
+  </si>
+  <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>rez_spv_003</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>rez_spv_004</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>rez_spv_005</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>rez_spv_006</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>rez_spv_007</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>rez_spv_008</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>rez_spv_009</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>rez_spv_010</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>rez_spv_011</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>rez_spv_012</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>rez_spv_013</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>rez_spv_014</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>rez_spv_015</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>rez_spv_016</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>rez_spv_017</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>rez_spv_018</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>rez_spv_019</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>rez_spv_020</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>rez_spv_021</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>rez_spv_022</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>rez_spv_023</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>rez_spv_024</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>rez_spv_025</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>rez_spv_026</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>rez_spv_027</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>rez_spv_028</t>
+  </si>
+  <si>
+    <t>elc_spv_028</t>
+  </si>
+  <si>
+    <t>rez_spv_029</t>
+  </si>
+  <si>
+    <t>elc_spv_029</t>
+  </si>
+  <si>
+    <t>rez_spv_030</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>rez_spv_031</t>
+  </si>
+  <si>
+    <t>elc_spv_031</t>
+  </si>
+  <si>
+    <t>rez_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>rez_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>rez_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>rez_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>rez_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>rez_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>rez_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>rez_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>rez_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>rez_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>rez_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>rez_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>rez_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>rez_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>rez_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>rez_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>rez_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>rez_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>rez_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>rez_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>rez_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>rez_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>rez_won_023</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>rez_won_024</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>rez_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>rez_won_026</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>rez_won_027</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>rez_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>rez_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>rez_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>rez_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>rez_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>rez_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>rez_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>rez_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>rez_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>rez_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>rez_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>rez_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>rez_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>rez_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>rez_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>rez_wof_012</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>rez_wof_013</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>rez_wof_014</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>rez_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>rez_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>rez_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>rez_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>rez_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>rez_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>rez_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>rez_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>rez_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>rez_wof_024</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>rez_wof_025</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>rez_wof_026</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>rez_wof_027</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>rez_wof_028</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>rez_wof_029</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>rez_wof_030</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>rez_wof_031</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>rez_wof_032</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>rez_wof_033</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>rez_wof_034</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>rez_wof_035</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>rez_wof_036</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>rez_wof_037</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>rez_wof_038</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>rez_wof_039</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>rez_wof_040</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>rez_wof_041</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>rez_wof_042</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>rez_wof_043</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>rez_wof_044</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
   </si>
 </sst>
 </file>
@@ -1168,6 +2915,4067 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6BE46C4-ED8B-4DE6-A784-DD4A4ACCB706}">
+  <dimension ref="B9:E298"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>162</v>
+      </c>
+      <c r="C40" t="s">
+        <v>163</v>
+      </c>
+      <c r="D40" t="s">
+        <v>163</v>
+      </c>
+      <c r="E40" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" t="s">
+        <v>169</v>
+      </c>
+      <c r="E43" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" t="s">
+        <v>177</v>
+      </c>
+      <c r="E47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" t="s">
+        <v>179</v>
+      </c>
+      <c r="D48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>180</v>
+      </c>
+      <c r="C49" t="s">
+        <v>181</v>
+      </c>
+      <c r="D49" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>182</v>
+      </c>
+      <c r="C50" t="s">
+        <v>183</v>
+      </c>
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C51" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>186</v>
+      </c>
+      <c r="C52" t="s">
+        <v>187</v>
+      </c>
+      <c r="D52" t="s">
+        <v>187</v>
+      </c>
+      <c r="E52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" t="s">
+        <v>191</v>
+      </c>
+      <c r="D54" t="s">
+        <v>191</v>
+      </c>
+      <c r="E54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" t="s">
+        <v>193</v>
+      </c>
+      <c r="D55" t="s">
+        <v>193</v>
+      </c>
+      <c r="E55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" t="s">
+        <v>195</v>
+      </c>
+      <c r="E56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" t="s">
+        <v>197</v>
+      </c>
+      <c r="E57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" t="s">
+        <v>199</v>
+      </c>
+      <c r="E58" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" t="s">
+        <v>201</v>
+      </c>
+      <c r="D59" t="s">
+        <v>201</v>
+      </c>
+      <c r="E59" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>202</v>
+      </c>
+      <c r="C60" t="s">
+        <v>203</v>
+      </c>
+      <c r="D60" t="s">
+        <v>203</v>
+      </c>
+      <c r="E60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" t="s">
+        <v>205</v>
+      </c>
+      <c r="D61" t="s">
+        <v>205</v>
+      </c>
+      <c r="E61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>206</v>
+      </c>
+      <c r="C62" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63" t="s">
+        <v>209</v>
+      </c>
+      <c r="D63" t="s">
+        <v>209</v>
+      </c>
+      <c r="E63" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>210</v>
+      </c>
+      <c r="C64" t="s">
+        <v>211</v>
+      </c>
+      <c r="D64" t="s">
+        <v>211</v>
+      </c>
+      <c r="E64" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>212</v>
+      </c>
+      <c r="C65" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" t="s">
+        <v>213</v>
+      </c>
+      <c r="E65" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>214</v>
+      </c>
+      <c r="C66" t="s">
+        <v>215</v>
+      </c>
+      <c r="D66" t="s">
+        <v>215</v>
+      </c>
+      <c r="E66" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" t="s">
+        <v>217</v>
+      </c>
+      <c r="E67" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>218</v>
+      </c>
+      <c r="C68" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" t="s">
+        <v>219</v>
+      </c>
+      <c r="E68" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" t="s">
+        <v>221</v>
+      </c>
+      <c r="E69" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>222</v>
+      </c>
+      <c r="C70" t="s">
+        <v>223</v>
+      </c>
+      <c r="D70" t="s">
+        <v>223</v>
+      </c>
+      <c r="E70" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" t="s">
+        <v>225</v>
+      </c>
+      <c r="E71" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>226</v>
+      </c>
+      <c r="C72" t="s">
+        <v>227</v>
+      </c>
+      <c r="D72" t="s">
+        <v>227</v>
+      </c>
+      <c r="E72" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>228</v>
+      </c>
+      <c r="C73" t="s">
+        <v>229</v>
+      </c>
+      <c r="D73" t="s">
+        <v>229</v>
+      </c>
+      <c r="E73" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>230</v>
+      </c>
+      <c r="C74" t="s">
+        <v>231</v>
+      </c>
+      <c r="D74" t="s">
+        <v>231</v>
+      </c>
+      <c r="E74" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>232</v>
+      </c>
+      <c r="C75" t="s">
+        <v>233</v>
+      </c>
+      <c r="D75" t="s">
+        <v>233</v>
+      </c>
+      <c r="E75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B76" t="s">
+        <v>234</v>
+      </c>
+      <c r="C76" t="s">
+        <v>235</v>
+      </c>
+      <c r="D76" t="s">
+        <v>235</v>
+      </c>
+      <c r="E76" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" t="s">
+        <v>237</v>
+      </c>
+      <c r="D77" t="s">
+        <v>237</v>
+      </c>
+      <c r="E77" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>238</v>
+      </c>
+      <c r="C78" t="s">
+        <v>239</v>
+      </c>
+      <c r="D78" t="s">
+        <v>239</v>
+      </c>
+      <c r="E78" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>240</v>
+      </c>
+      <c r="C79" t="s">
+        <v>241</v>
+      </c>
+      <c r="D79" t="s">
+        <v>241</v>
+      </c>
+      <c r="E79" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>242</v>
+      </c>
+      <c r="C80" t="s">
+        <v>243</v>
+      </c>
+      <c r="D80" t="s">
+        <v>243</v>
+      </c>
+      <c r="E80" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
+        <v>244</v>
+      </c>
+      <c r="C81" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81" t="s">
+        <v>245</v>
+      </c>
+      <c r="E81" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B82" t="s">
+        <v>246</v>
+      </c>
+      <c r="C82" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82" t="s">
+        <v>247</v>
+      </c>
+      <c r="E82" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B83" t="s">
+        <v>248</v>
+      </c>
+      <c r="C83" t="s">
+        <v>249</v>
+      </c>
+      <c r="D83" t="s">
+        <v>249</v>
+      </c>
+      <c r="E83" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
+        <v>250</v>
+      </c>
+      <c r="C84" t="s">
+        <v>251</v>
+      </c>
+      <c r="D84" t="s">
+        <v>251</v>
+      </c>
+      <c r="E84" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85" t="s">
+        <v>253</v>
+      </c>
+      <c r="D85" t="s">
+        <v>253</v>
+      </c>
+      <c r="E85" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" t="s">
+        <v>255</v>
+      </c>
+      <c r="E86" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B87" t="s">
+        <v>256</v>
+      </c>
+      <c r="C87" t="s">
+        <v>257</v>
+      </c>
+      <c r="D87" t="s">
+        <v>257</v>
+      </c>
+      <c r="E87" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B88" t="s">
+        <v>258</v>
+      </c>
+      <c r="C88" t="s">
+        <v>259</v>
+      </c>
+      <c r="D88" t="s">
+        <v>259</v>
+      </c>
+      <c r="E88" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B89" t="s">
+        <v>260</v>
+      </c>
+      <c r="C89" t="s">
+        <v>261</v>
+      </c>
+      <c r="D89" t="s">
+        <v>261</v>
+      </c>
+      <c r="E89" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B90" t="s">
+        <v>262</v>
+      </c>
+      <c r="C90" t="s">
+        <v>263</v>
+      </c>
+      <c r="D90" t="s">
+        <v>263</v>
+      </c>
+      <c r="E90" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B91" t="s">
+        <v>264</v>
+      </c>
+      <c r="C91" t="s">
+        <v>265</v>
+      </c>
+      <c r="D91" t="s">
+        <v>265</v>
+      </c>
+      <c r="E91" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B92" t="s">
+        <v>266</v>
+      </c>
+      <c r="C92" t="s">
+        <v>267</v>
+      </c>
+      <c r="D92" t="s">
+        <v>267</v>
+      </c>
+      <c r="E92" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B93" t="s">
+        <v>268</v>
+      </c>
+      <c r="C93" t="s">
+        <v>269</v>
+      </c>
+      <c r="D93" t="s">
+        <v>269</v>
+      </c>
+      <c r="E93" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B94" t="s">
+        <v>270</v>
+      </c>
+      <c r="C94" t="s">
+        <v>271</v>
+      </c>
+      <c r="D94" t="s">
+        <v>271</v>
+      </c>
+      <c r="E94" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B95" t="s">
+        <v>272</v>
+      </c>
+      <c r="C95" t="s">
+        <v>273</v>
+      </c>
+      <c r="D95" t="s">
+        <v>273</v>
+      </c>
+      <c r="E95" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B96" t="s">
+        <v>274</v>
+      </c>
+      <c r="C96" t="s">
+        <v>275</v>
+      </c>
+      <c r="D96" t="s">
+        <v>275</v>
+      </c>
+      <c r="E96" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B97" t="s">
+        <v>276</v>
+      </c>
+      <c r="C97" t="s">
+        <v>277</v>
+      </c>
+      <c r="D97" t="s">
+        <v>277</v>
+      </c>
+      <c r="E97" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B98" t="s">
+        <v>278</v>
+      </c>
+      <c r="C98" t="s">
+        <v>279</v>
+      </c>
+      <c r="D98" t="s">
+        <v>279</v>
+      </c>
+      <c r="E98" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B99" t="s">
+        <v>280</v>
+      </c>
+      <c r="C99" t="s">
+        <v>281</v>
+      </c>
+      <c r="D99" t="s">
+        <v>281</v>
+      </c>
+      <c r="E99" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B100" t="s">
+        <v>282</v>
+      </c>
+      <c r="C100" t="s">
+        <v>283</v>
+      </c>
+      <c r="D100" t="s">
+        <v>283</v>
+      </c>
+      <c r="E100" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B101" t="s">
+        <v>284</v>
+      </c>
+      <c r="C101" t="s">
+        <v>285</v>
+      </c>
+      <c r="D101" t="s">
+        <v>285</v>
+      </c>
+      <c r="E101" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B102" t="s">
+        <v>286</v>
+      </c>
+      <c r="C102" t="s">
+        <v>287</v>
+      </c>
+      <c r="D102" t="s">
+        <v>287</v>
+      </c>
+      <c r="E102" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B103" t="s">
+        <v>288</v>
+      </c>
+      <c r="C103" t="s">
+        <v>289</v>
+      </c>
+      <c r="D103" t="s">
+        <v>289</v>
+      </c>
+      <c r="E103" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B104" t="s">
+        <v>290</v>
+      </c>
+      <c r="C104" t="s">
+        <v>291</v>
+      </c>
+      <c r="D104" t="s">
+        <v>291</v>
+      </c>
+      <c r="E104" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B105" t="s">
+        <v>292</v>
+      </c>
+      <c r="C105" t="s">
+        <v>293</v>
+      </c>
+      <c r="D105" t="s">
+        <v>293</v>
+      </c>
+      <c r="E105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B106" t="s">
+        <v>294</v>
+      </c>
+      <c r="C106" t="s">
+        <v>295</v>
+      </c>
+      <c r="D106" t="s">
+        <v>295</v>
+      </c>
+      <c r="E106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B107" t="s">
+        <v>296</v>
+      </c>
+      <c r="C107" t="s">
+        <v>297</v>
+      </c>
+      <c r="D107" t="s">
+        <v>297</v>
+      </c>
+      <c r="E107" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B108" t="s">
+        <v>298</v>
+      </c>
+      <c r="C108" t="s">
+        <v>299</v>
+      </c>
+      <c r="D108" t="s">
+        <v>299</v>
+      </c>
+      <c r="E108" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B109" t="s">
+        <v>300</v>
+      </c>
+      <c r="C109" t="s">
+        <v>301</v>
+      </c>
+      <c r="D109" t="s">
+        <v>301</v>
+      </c>
+      <c r="E109" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B110" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" t="s">
+        <v>303</v>
+      </c>
+      <c r="D110" t="s">
+        <v>303</v>
+      </c>
+      <c r="E110" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B111" t="s">
+        <v>304</v>
+      </c>
+      <c r="C111" t="s">
+        <v>305</v>
+      </c>
+      <c r="D111" t="s">
+        <v>305</v>
+      </c>
+      <c r="E111" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B112" t="s">
+        <v>306</v>
+      </c>
+      <c r="C112" t="s">
+        <v>307</v>
+      </c>
+      <c r="D112" t="s">
+        <v>307</v>
+      </c>
+      <c r="E112" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B113" t="s">
+        <v>308</v>
+      </c>
+      <c r="C113" t="s">
+        <v>309</v>
+      </c>
+      <c r="D113" t="s">
+        <v>309</v>
+      </c>
+      <c r="E113" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B114" t="s">
+        <v>310</v>
+      </c>
+      <c r="C114" t="s">
+        <v>311</v>
+      </c>
+      <c r="D114" t="s">
+        <v>311</v>
+      </c>
+      <c r="E114" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B115" t="s">
+        <v>312</v>
+      </c>
+      <c r="C115" t="s">
+        <v>313</v>
+      </c>
+      <c r="D115" t="s">
+        <v>313</v>
+      </c>
+      <c r="E115" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B116" t="s">
+        <v>314</v>
+      </c>
+      <c r="C116" t="s">
+        <v>315</v>
+      </c>
+      <c r="D116" t="s">
+        <v>315</v>
+      </c>
+      <c r="E116" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B117" t="s">
+        <v>316</v>
+      </c>
+      <c r="C117" t="s">
+        <v>317</v>
+      </c>
+      <c r="D117" t="s">
+        <v>317</v>
+      </c>
+      <c r="E117" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B118" t="s">
+        <v>318</v>
+      </c>
+      <c r="C118" t="s">
+        <v>319</v>
+      </c>
+      <c r="D118" t="s">
+        <v>319</v>
+      </c>
+      <c r="E118" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B119" t="s">
+        <v>320</v>
+      </c>
+      <c r="C119" t="s">
+        <v>321</v>
+      </c>
+      <c r="D119" t="s">
+        <v>321</v>
+      </c>
+      <c r="E119" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B120" t="s">
+        <v>322</v>
+      </c>
+      <c r="C120" t="s">
+        <v>323</v>
+      </c>
+      <c r="D120" t="s">
+        <v>323</v>
+      </c>
+      <c r="E120" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B121" t="s">
+        <v>324</v>
+      </c>
+      <c r="C121" t="s">
+        <v>325</v>
+      </c>
+      <c r="D121" t="s">
+        <v>325</v>
+      </c>
+      <c r="E121" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B122" t="s">
+        <v>326</v>
+      </c>
+      <c r="C122" t="s">
+        <v>327</v>
+      </c>
+      <c r="D122" t="s">
+        <v>327</v>
+      </c>
+      <c r="E122" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B123" t="s">
+        <v>328</v>
+      </c>
+      <c r="C123" t="s">
+        <v>329</v>
+      </c>
+      <c r="D123" t="s">
+        <v>329</v>
+      </c>
+      <c r="E123" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B124" t="s">
+        <v>330</v>
+      </c>
+      <c r="C124" t="s">
+        <v>331</v>
+      </c>
+      <c r="D124" t="s">
+        <v>331</v>
+      </c>
+      <c r="E124" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B125" t="s">
+        <v>332</v>
+      </c>
+      <c r="C125" t="s">
+        <v>333</v>
+      </c>
+      <c r="D125" t="s">
+        <v>333</v>
+      </c>
+      <c r="E125" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B126" t="s">
+        <v>334</v>
+      </c>
+      <c r="C126" t="s">
+        <v>335</v>
+      </c>
+      <c r="D126" t="s">
+        <v>335</v>
+      </c>
+      <c r="E126" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B127" t="s">
+        <v>336</v>
+      </c>
+      <c r="C127" t="s">
+        <v>337</v>
+      </c>
+      <c r="D127" t="s">
+        <v>337</v>
+      </c>
+      <c r="E127" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B128" t="s">
+        <v>338</v>
+      </c>
+      <c r="C128" t="s">
+        <v>339</v>
+      </c>
+      <c r="D128" t="s">
+        <v>339</v>
+      </c>
+      <c r="E128" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B129" t="s">
+        <v>340</v>
+      </c>
+      <c r="C129" t="s">
+        <v>341</v>
+      </c>
+      <c r="D129" t="s">
+        <v>341</v>
+      </c>
+      <c r="E129" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B130" t="s">
+        <v>342</v>
+      </c>
+      <c r="C130" t="s">
+        <v>343</v>
+      </c>
+      <c r="D130" t="s">
+        <v>343</v>
+      </c>
+      <c r="E130" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B131" t="s">
+        <v>344</v>
+      </c>
+      <c r="C131" t="s">
+        <v>345</v>
+      </c>
+      <c r="D131" t="s">
+        <v>345</v>
+      </c>
+      <c r="E131" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B132" t="s">
+        <v>346</v>
+      </c>
+      <c r="C132" t="s">
+        <v>347</v>
+      </c>
+      <c r="D132" t="s">
+        <v>347</v>
+      </c>
+      <c r="E132" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B133" t="s">
+        <v>348</v>
+      </c>
+      <c r="C133" t="s">
+        <v>349</v>
+      </c>
+      <c r="D133" t="s">
+        <v>349</v>
+      </c>
+      <c r="E133" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B134" t="s">
+        <v>350</v>
+      </c>
+      <c r="C134" t="s">
+        <v>351</v>
+      </c>
+      <c r="D134" t="s">
+        <v>351</v>
+      </c>
+      <c r="E134" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B135" t="s">
+        <v>352</v>
+      </c>
+      <c r="C135" t="s">
+        <v>353</v>
+      </c>
+      <c r="D135" t="s">
+        <v>353</v>
+      </c>
+      <c r="E135" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B136" t="s">
+        <v>354</v>
+      </c>
+      <c r="C136" t="s">
+        <v>355</v>
+      </c>
+      <c r="D136" t="s">
+        <v>355</v>
+      </c>
+      <c r="E136" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B137" t="s">
+        <v>356</v>
+      </c>
+      <c r="C137" t="s">
+        <v>357</v>
+      </c>
+      <c r="D137" t="s">
+        <v>357</v>
+      </c>
+      <c r="E137" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B138" t="s">
+        <v>358</v>
+      </c>
+      <c r="C138" t="s">
+        <v>359</v>
+      </c>
+      <c r="D138" t="s">
+        <v>359</v>
+      </c>
+      <c r="E138" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B139" t="s">
+        <v>360</v>
+      </c>
+      <c r="C139" t="s">
+        <v>361</v>
+      </c>
+      <c r="D139" t="s">
+        <v>361</v>
+      </c>
+      <c r="E139" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B140" t="s">
+        <v>362</v>
+      </c>
+      <c r="C140" t="s">
+        <v>363</v>
+      </c>
+      <c r="D140" t="s">
+        <v>363</v>
+      </c>
+      <c r="E140" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B141" t="s">
+        <v>364</v>
+      </c>
+      <c r="C141" t="s">
+        <v>365</v>
+      </c>
+      <c r="D141" t="s">
+        <v>365</v>
+      </c>
+      <c r="E141" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B142" t="s">
+        <v>366</v>
+      </c>
+      <c r="C142" t="s">
+        <v>367</v>
+      </c>
+      <c r="D142" t="s">
+        <v>367</v>
+      </c>
+      <c r="E142" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B143" t="s">
+        <v>368</v>
+      </c>
+      <c r="C143" t="s">
+        <v>369</v>
+      </c>
+      <c r="D143" t="s">
+        <v>369</v>
+      </c>
+      <c r="E143" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B144" t="s">
+        <v>370</v>
+      </c>
+      <c r="C144" t="s">
+        <v>371</v>
+      </c>
+      <c r="D144" t="s">
+        <v>371</v>
+      </c>
+      <c r="E144" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B145" t="s">
+        <v>372</v>
+      </c>
+      <c r="C145" t="s">
+        <v>373</v>
+      </c>
+      <c r="D145" t="s">
+        <v>373</v>
+      </c>
+      <c r="E145" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B146" t="s">
+        <v>374</v>
+      </c>
+      <c r="C146" t="s">
+        <v>375</v>
+      </c>
+      <c r="D146" t="s">
+        <v>375</v>
+      </c>
+      <c r="E146" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B147" t="s">
+        <v>376</v>
+      </c>
+      <c r="C147" t="s">
+        <v>377</v>
+      </c>
+      <c r="D147" t="s">
+        <v>377</v>
+      </c>
+      <c r="E147" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B148" t="s">
+        <v>378</v>
+      </c>
+      <c r="C148" t="s">
+        <v>379</v>
+      </c>
+      <c r="D148" t="s">
+        <v>379</v>
+      </c>
+      <c r="E148" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B149" t="s">
+        <v>380</v>
+      </c>
+      <c r="C149" t="s">
+        <v>381</v>
+      </c>
+      <c r="D149" t="s">
+        <v>381</v>
+      </c>
+      <c r="E149" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B150" t="s">
+        <v>382</v>
+      </c>
+      <c r="C150" t="s">
+        <v>383</v>
+      </c>
+      <c r="D150" t="s">
+        <v>383</v>
+      </c>
+      <c r="E150" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B151" t="s">
+        <v>384</v>
+      </c>
+      <c r="C151" t="s">
+        <v>385</v>
+      </c>
+      <c r="D151" t="s">
+        <v>385</v>
+      </c>
+      <c r="E151" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B152" t="s">
+        <v>386</v>
+      </c>
+      <c r="C152" t="s">
+        <v>387</v>
+      </c>
+      <c r="D152" t="s">
+        <v>387</v>
+      </c>
+      <c r="E152" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B153" t="s">
+        <v>388</v>
+      </c>
+      <c r="C153" t="s">
+        <v>389</v>
+      </c>
+      <c r="D153" t="s">
+        <v>389</v>
+      </c>
+      <c r="E153" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B154" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" t="s">
+        <v>391</v>
+      </c>
+      <c r="D154" t="s">
+        <v>391</v>
+      </c>
+      <c r="E154" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B155" t="s">
+        <v>392</v>
+      </c>
+      <c r="C155" t="s">
+        <v>393</v>
+      </c>
+      <c r="D155" t="s">
+        <v>393</v>
+      </c>
+      <c r="E155" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B156" t="s">
+        <v>394</v>
+      </c>
+      <c r="C156" t="s">
+        <v>395</v>
+      </c>
+      <c r="D156" t="s">
+        <v>395</v>
+      </c>
+      <c r="E156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B157" t="s">
+        <v>396</v>
+      </c>
+      <c r="C157" t="s">
+        <v>397</v>
+      </c>
+      <c r="D157" t="s">
+        <v>397</v>
+      </c>
+      <c r="E157" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B158" t="s">
+        <v>398</v>
+      </c>
+      <c r="C158" t="s">
+        <v>399</v>
+      </c>
+      <c r="D158" t="s">
+        <v>399</v>
+      </c>
+      <c r="E158" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B159" t="s">
+        <v>400</v>
+      </c>
+      <c r="C159" t="s">
+        <v>401</v>
+      </c>
+      <c r="D159" t="s">
+        <v>401</v>
+      </c>
+      <c r="E159" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B160" t="s">
+        <v>402</v>
+      </c>
+      <c r="C160" t="s">
+        <v>403</v>
+      </c>
+      <c r="D160" t="s">
+        <v>403</v>
+      </c>
+      <c r="E160" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B161" t="s">
+        <v>404</v>
+      </c>
+      <c r="C161" t="s">
+        <v>405</v>
+      </c>
+      <c r="D161" t="s">
+        <v>405</v>
+      </c>
+      <c r="E161" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B162" t="s">
+        <v>406</v>
+      </c>
+      <c r="C162" t="s">
+        <v>407</v>
+      </c>
+      <c r="D162" t="s">
+        <v>407</v>
+      </c>
+      <c r="E162" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B163" t="s">
+        <v>408</v>
+      </c>
+      <c r="C163" t="s">
+        <v>409</v>
+      </c>
+      <c r="D163" t="s">
+        <v>409</v>
+      </c>
+      <c r="E163" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B164" t="s">
+        <v>410</v>
+      </c>
+      <c r="C164" t="s">
+        <v>411</v>
+      </c>
+      <c r="D164" t="s">
+        <v>411</v>
+      </c>
+      <c r="E164" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B165" t="s">
+        <v>412</v>
+      </c>
+      <c r="C165" t="s">
+        <v>413</v>
+      </c>
+      <c r="D165" t="s">
+        <v>413</v>
+      </c>
+      <c r="E165" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B166" t="s">
+        <v>414</v>
+      </c>
+      <c r="C166" t="s">
+        <v>415</v>
+      </c>
+      <c r="D166" t="s">
+        <v>415</v>
+      </c>
+      <c r="E166" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B167" t="s">
+        <v>416</v>
+      </c>
+      <c r="C167" t="s">
+        <v>417</v>
+      </c>
+      <c r="D167" t="s">
+        <v>417</v>
+      </c>
+      <c r="E167" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B168" t="s">
+        <v>418</v>
+      </c>
+      <c r="C168" t="s">
+        <v>419</v>
+      </c>
+      <c r="D168" t="s">
+        <v>419</v>
+      </c>
+      <c r="E168" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B169" t="s">
+        <v>420</v>
+      </c>
+      <c r="C169" t="s">
+        <v>421</v>
+      </c>
+      <c r="D169" t="s">
+        <v>421</v>
+      </c>
+      <c r="E169" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B170" t="s">
+        <v>422</v>
+      </c>
+      <c r="C170" t="s">
+        <v>423</v>
+      </c>
+      <c r="D170" t="s">
+        <v>423</v>
+      </c>
+      <c r="E170" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B171" t="s">
+        <v>424</v>
+      </c>
+      <c r="C171" t="s">
+        <v>425</v>
+      </c>
+      <c r="D171" t="s">
+        <v>425</v>
+      </c>
+      <c r="E171" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B172" t="s">
+        <v>426</v>
+      </c>
+      <c r="C172" t="s">
+        <v>427</v>
+      </c>
+      <c r="D172" t="s">
+        <v>427</v>
+      </c>
+      <c r="E172" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B173" t="s">
+        <v>428</v>
+      </c>
+      <c r="C173" t="s">
+        <v>429</v>
+      </c>
+      <c r="D173" t="s">
+        <v>429</v>
+      </c>
+      <c r="E173" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B174" t="s">
+        <v>430</v>
+      </c>
+      <c r="C174" t="s">
+        <v>431</v>
+      </c>
+      <c r="D174" t="s">
+        <v>431</v>
+      </c>
+      <c r="E174" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B175" t="s">
+        <v>432</v>
+      </c>
+      <c r="C175" t="s">
+        <v>433</v>
+      </c>
+      <c r="D175" t="s">
+        <v>433</v>
+      </c>
+      <c r="E175" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B176" t="s">
+        <v>434</v>
+      </c>
+      <c r="C176" t="s">
+        <v>435</v>
+      </c>
+      <c r="D176" t="s">
+        <v>435</v>
+      </c>
+      <c r="E176" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B177" t="s">
+        <v>436</v>
+      </c>
+      <c r="C177" t="s">
+        <v>437</v>
+      </c>
+      <c r="D177" t="s">
+        <v>437</v>
+      </c>
+      <c r="E177" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B178" t="s">
+        <v>438</v>
+      </c>
+      <c r="C178" t="s">
+        <v>439</v>
+      </c>
+      <c r="D178" t="s">
+        <v>439</v>
+      </c>
+      <c r="E178" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B179" t="s">
+        <v>440</v>
+      </c>
+      <c r="C179" t="s">
+        <v>441</v>
+      </c>
+      <c r="D179" t="s">
+        <v>441</v>
+      </c>
+      <c r="E179" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B180" t="s">
+        <v>442</v>
+      </c>
+      <c r="C180" t="s">
+        <v>443</v>
+      </c>
+      <c r="D180" t="s">
+        <v>443</v>
+      </c>
+      <c r="E180" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B181" t="s">
+        <v>444</v>
+      </c>
+      <c r="C181" t="s">
+        <v>445</v>
+      </c>
+      <c r="D181" t="s">
+        <v>445</v>
+      </c>
+      <c r="E181" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B182" t="s">
+        <v>446</v>
+      </c>
+      <c r="C182" t="s">
+        <v>447</v>
+      </c>
+      <c r="D182" t="s">
+        <v>447</v>
+      </c>
+      <c r="E182" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B183" t="s">
+        <v>448</v>
+      </c>
+      <c r="C183" t="s">
+        <v>449</v>
+      </c>
+      <c r="D183" t="s">
+        <v>449</v>
+      </c>
+      <c r="E183" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B184" t="s">
+        <v>450</v>
+      </c>
+      <c r="C184" t="s">
+        <v>451</v>
+      </c>
+      <c r="D184" t="s">
+        <v>451</v>
+      </c>
+      <c r="E184" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="185" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B185" t="s">
+        <v>452</v>
+      </c>
+      <c r="C185" t="s">
+        <v>453</v>
+      </c>
+      <c r="D185" t="s">
+        <v>453</v>
+      </c>
+      <c r="E185" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="186" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B186" t="s">
+        <v>454</v>
+      </c>
+      <c r="C186" t="s">
+        <v>455</v>
+      </c>
+      <c r="D186" t="s">
+        <v>455</v>
+      </c>
+      <c r="E186" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B187" t="s">
+        <v>456</v>
+      </c>
+      <c r="C187" t="s">
+        <v>457</v>
+      </c>
+      <c r="D187" t="s">
+        <v>457</v>
+      </c>
+      <c r="E187" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B188" t="s">
+        <v>458</v>
+      </c>
+      <c r="C188" t="s">
+        <v>459</v>
+      </c>
+      <c r="D188" t="s">
+        <v>459</v>
+      </c>
+      <c r="E188" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="189" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B189" t="s">
+        <v>460</v>
+      </c>
+      <c r="C189" t="s">
+        <v>461</v>
+      </c>
+      <c r="D189" t="s">
+        <v>461</v>
+      </c>
+      <c r="E189" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B190" t="s">
+        <v>462</v>
+      </c>
+      <c r="C190" t="s">
+        <v>463</v>
+      </c>
+      <c r="D190" t="s">
+        <v>463</v>
+      </c>
+      <c r="E190" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="191" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B191" t="s">
+        <v>464</v>
+      </c>
+      <c r="C191" t="s">
+        <v>465</v>
+      </c>
+      <c r="D191" t="s">
+        <v>465</v>
+      </c>
+      <c r="E191" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="192" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B192" t="s">
+        <v>466</v>
+      </c>
+      <c r="C192" t="s">
+        <v>467</v>
+      </c>
+      <c r="D192" t="s">
+        <v>467</v>
+      </c>
+      <c r="E192" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="193" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B193" t="s">
+        <v>468</v>
+      </c>
+      <c r="C193" t="s">
+        <v>469</v>
+      </c>
+      <c r="D193" t="s">
+        <v>469</v>
+      </c>
+      <c r="E193" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B194" t="s">
+        <v>470</v>
+      </c>
+      <c r="C194" t="s">
+        <v>471</v>
+      </c>
+      <c r="D194" t="s">
+        <v>471</v>
+      </c>
+      <c r="E194" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B195" t="s">
+        <v>472</v>
+      </c>
+      <c r="C195" t="s">
+        <v>473</v>
+      </c>
+      <c r="D195" t="s">
+        <v>473</v>
+      </c>
+      <c r="E195" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B196" t="s">
+        <v>474</v>
+      </c>
+      <c r="C196" t="s">
+        <v>475</v>
+      </c>
+      <c r="D196" t="s">
+        <v>475</v>
+      </c>
+      <c r="E196" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B197" t="s">
+        <v>476</v>
+      </c>
+      <c r="C197" t="s">
+        <v>477</v>
+      </c>
+      <c r="D197" t="s">
+        <v>477</v>
+      </c>
+      <c r="E197" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B198" t="s">
+        <v>478</v>
+      </c>
+      <c r="C198" t="s">
+        <v>479</v>
+      </c>
+      <c r="D198" t="s">
+        <v>479</v>
+      </c>
+      <c r="E198" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B199" t="s">
+        <v>480</v>
+      </c>
+      <c r="C199" t="s">
+        <v>481</v>
+      </c>
+      <c r="D199" t="s">
+        <v>481</v>
+      </c>
+      <c r="E199" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B200" t="s">
+        <v>482</v>
+      </c>
+      <c r="C200" t="s">
+        <v>483</v>
+      </c>
+      <c r="D200" t="s">
+        <v>483</v>
+      </c>
+      <c r="E200" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B201" t="s">
+        <v>484</v>
+      </c>
+      <c r="C201" t="s">
+        <v>485</v>
+      </c>
+      <c r="D201" t="s">
+        <v>485</v>
+      </c>
+      <c r="E201" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="202" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B202" t="s">
+        <v>486</v>
+      </c>
+      <c r="C202" t="s">
+        <v>487</v>
+      </c>
+      <c r="D202" t="s">
+        <v>487</v>
+      </c>
+      <c r="E202" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B203" t="s">
+        <v>488</v>
+      </c>
+      <c r="C203" t="s">
+        <v>489</v>
+      </c>
+      <c r="D203" t="s">
+        <v>489</v>
+      </c>
+      <c r="E203" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B204" t="s">
+        <v>490</v>
+      </c>
+      <c r="C204" t="s">
+        <v>491</v>
+      </c>
+      <c r="D204" t="s">
+        <v>491</v>
+      </c>
+      <c r="E204" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B205" t="s">
+        <v>492</v>
+      </c>
+      <c r="C205" t="s">
+        <v>493</v>
+      </c>
+      <c r="D205" t="s">
+        <v>493</v>
+      </c>
+      <c r="E205" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B206" t="s">
+        <v>494</v>
+      </c>
+      <c r="C206" t="s">
+        <v>495</v>
+      </c>
+      <c r="D206" t="s">
+        <v>495</v>
+      </c>
+      <c r="E206" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B207" t="s">
+        <v>496</v>
+      </c>
+      <c r="C207" t="s">
+        <v>497</v>
+      </c>
+      <c r="D207" t="s">
+        <v>497</v>
+      </c>
+      <c r="E207" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B208" t="s">
+        <v>498</v>
+      </c>
+      <c r="C208" t="s">
+        <v>499</v>
+      </c>
+      <c r="D208" t="s">
+        <v>499</v>
+      </c>
+      <c r="E208" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B209" t="s">
+        <v>500</v>
+      </c>
+      <c r="C209" t="s">
+        <v>501</v>
+      </c>
+      <c r="D209" t="s">
+        <v>501</v>
+      </c>
+      <c r="E209" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B210" t="s">
+        <v>502</v>
+      </c>
+      <c r="C210" t="s">
+        <v>503</v>
+      </c>
+      <c r="D210" t="s">
+        <v>503</v>
+      </c>
+      <c r="E210" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="211" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B211" t="s">
+        <v>504</v>
+      </c>
+      <c r="C211" t="s">
+        <v>505</v>
+      </c>
+      <c r="D211" t="s">
+        <v>505</v>
+      </c>
+      <c r="E211" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B212" t="s">
+        <v>506</v>
+      </c>
+      <c r="C212" t="s">
+        <v>507</v>
+      </c>
+      <c r="D212" t="s">
+        <v>507</v>
+      </c>
+      <c r="E212" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="213" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B213" t="s">
+        <v>508</v>
+      </c>
+      <c r="C213" t="s">
+        <v>509</v>
+      </c>
+      <c r="D213" t="s">
+        <v>509</v>
+      </c>
+      <c r="E213" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B214" t="s">
+        <v>510</v>
+      </c>
+      <c r="C214" t="s">
+        <v>511</v>
+      </c>
+      <c r="D214" t="s">
+        <v>511</v>
+      </c>
+      <c r="E214" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="215" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B215" t="s">
+        <v>512</v>
+      </c>
+      <c r="C215" t="s">
+        <v>513</v>
+      </c>
+      <c r="D215" t="s">
+        <v>513</v>
+      </c>
+      <c r="E215" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B216" t="s">
+        <v>514</v>
+      </c>
+      <c r="C216" t="s">
+        <v>515</v>
+      </c>
+      <c r="D216" t="s">
+        <v>515</v>
+      </c>
+      <c r="E216" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="217" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B217" t="s">
+        <v>516</v>
+      </c>
+      <c r="C217" t="s">
+        <v>517</v>
+      </c>
+      <c r="D217" t="s">
+        <v>517</v>
+      </c>
+      <c r="E217" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B218" t="s">
+        <v>518</v>
+      </c>
+      <c r="C218" t="s">
+        <v>519</v>
+      </c>
+      <c r="D218" t="s">
+        <v>519</v>
+      </c>
+      <c r="E218" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="219" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B219" t="s">
+        <v>520</v>
+      </c>
+      <c r="C219" t="s">
+        <v>521</v>
+      </c>
+      <c r="D219" t="s">
+        <v>521</v>
+      </c>
+      <c r="E219" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="220" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B220" t="s">
+        <v>522</v>
+      </c>
+      <c r="C220" t="s">
+        <v>523</v>
+      </c>
+      <c r="D220" t="s">
+        <v>523</v>
+      </c>
+      <c r="E220" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="221" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B221" t="s">
+        <v>524</v>
+      </c>
+      <c r="C221" t="s">
+        <v>525</v>
+      </c>
+      <c r="D221" t="s">
+        <v>525</v>
+      </c>
+      <c r="E221" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="222" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B222" t="s">
+        <v>526</v>
+      </c>
+      <c r="C222" t="s">
+        <v>527</v>
+      </c>
+      <c r="D222" t="s">
+        <v>527</v>
+      </c>
+      <c r="E222" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="223" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B223" t="s">
+        <v>528</v>
+      </c>
+      <c r="C223" t="s">
+        <v>529</v>
+      </c>
+      <c r="D223" t="s">
+        <v>529</v>
+      </c>
+      <c r="E223" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="224" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B224" t="s">
+        <v>530</v>
+      </c>
+      <c r="C224" t="s">
+        <v>531</v>
+      </c>
+      <c r="D224" t="s">
+        <v>531</v>
+      </c>
+      <c r="E224" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="225" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B225" t="s">
+        <v>532</v>
+      </c>
+      <c r="C225" t="s">
+        <v>533</v>
+      </c>
+      <c r="D225" t="s">
+        <v>533</v>
+      </c>
+      <c r="E225" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B226" t="s">
+        <v>534</v>
+      </c>
+      <c r="C226" t="s">
+        <v>535</v>
+      </c>
+      <c r="D226" t="s">
+        <v>535</v>
+      </c>
+      <c r="E226" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B227" t="s">
+        <v>536</v>
+      </c>
+      <c r="C227" t="s">
+        <v>537</v>
+      </c>
+      <c r="D227" t="s">
+        <v>537</v>
+      </c>
+      <c r="E227" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B228" t="s">
+        <v>538</v>
+      </c>
+      <c r="C228" t="s">
+        <v>539</v>
+      </c>
+      <c r="D228" t="s">
+        <v>539</v>
+      </c>
+      <c r="E228" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B229" t="s">
+        <v>540</v>
+      </c>
+      <c r="C229" t="s">
+        <v>541</v>
+      </c>
+      <c r="D229" t="s">
+        <v>541</v>
+      </c>
+      <c r="E229" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B230" t="s">
+        <v>542</v>
+      </c>
+      <c r="C230" t="s">
+        <v>543</v>
+      </c>
+      <c r="D230" t="s">
+        <v>543</v>
+      </c>
+      <c r="E230" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="231" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B231" t="s">
+        <v>544</v>
+      </c>
+      <c r="C231" t="s">
+        <v>545</v>
+      </c>
+      <c r="D231" t="s">
+        <v>545</v>
+      </c>
+      <c r="E231" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B232" t="s">
+        <v>546</v>
+      </c>
+      <c r="C232" t="s">
+        <v>547</v>
+      </c>
+      <c r="D232" t="s">
+        <v>547</v>
+      </c>
+      <c r="E232" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="233" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B233" t="s">
+        <v>548</v>
+      </c>
+      <c r="C233" t="s">
+        <v>549</v>
+      </c>
+      <c r="D233" t="s">
+        <v>549</v>
+      </c>
+      <c r="E233" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="234" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B234" t="s">
+        <v>550</v>
+      </c>
+      <c r="C234" t="s">
+        <v>551</v>
+      </c>
+      <c r="D234" t="s">
+        <v>551</v>
+      </c>
+      <c r="E234" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="235" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B235" t="s">
+        <v>552</v>
+      </c>
+      <c r="C235" t="s">
+        <v>553</v>
+      </c>
+      <c r="D235" t="s">
+        <v>553</v>
+      </c>
+      <c r="E235" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="236" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B236" t="s">
+        <v>554</v>
+      </c>
+      <c r="C236" t="s">
+        <v>555</v>
+      </c>
+      <c r="D236" t="s">
+        <v>555</v>
+      </c>
+      <c r="E236" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="237" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B237" t="s">
+        <v>556</v>
+      </c>
+      <c r="C237" t="s">
+        <v>557</v>
+      </c>
+      <c r="D237" t="s">
+        <v>557</v>
+      </c>
+      <c r="E237" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="238" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B238" t="s">
+        <v>558</v>
+      </c>
+      <c r="C238" t="s">
+        <v>559</v>
+      </c>
+      <c r="D238" t="s">
+        <v>559</v>
+      </c>
+      <c r="E238" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="239" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B239" t="s">
+        <v>560</v>
+      </c>
+      <c r="C239" t="s">
+        <v>561</v>
+      </c>
+      <c r="D239" t="s">
+        <v>561</v>
+      </c>
+      <c r="E239" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="240" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B240" t="s">
+        <v>562</v>
+      </c>
+      <c r="C240" t="s">
+        <v>563</v>
+      </c>
+      <c r="D240" t="s">
+        <v>563</v>
+      </c>
+      <c r="E240" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="241" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B241" t="s">
+        <v>564</v>
+      </c>
+      <c r="C241" t="s">
+        <v>565</v>
+      </c>
+      <c r="D241" t="s">
+        <v>565</v>
+      </c>
+      <c r="E241" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="242" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B242" t="s">
+        <v>566</v>
+      </c>
+      <c r="C242" t="s">
+        <v>567</v>
+      </c>
+      <c r="D242" t="s">
+        <v>567</v>
+      </c>
+      <c r="E242" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="243" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B243" t="s">
+        <v>568</v>
+      </c>
+      <c r="C243" t="s">
+        <v>569</v>
+      </c>
+      <c r="D243" t="s">
+        <v>569</v>
+      </c>
+      <c r="E243" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="244" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B244" t="s">
+        <v>570</v>
+      </c>
+      <c r="C244" t="s">
+        <v>571</v>
+      </c>
+      <c r="D244" t="s">
+        <v>571</v>
+      </c>
+      <c r="E244" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="245" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B245" t="s">
+        <v>572</v>
+      </c>
+      <c r="C245" t="s">
+        <v>573</v>
+      </c>
+      <c r="D245" t="s">
+        <v>573</v>
+      </c>
+      <c r="E245" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="246" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B246" t="s">
+        <v>574</v>
+      </c>
+      <c r="C246" t="s">
+        <v>575</v>
+      </c>
+      <c r="D246" t="s">
+        <v>575</v>
+      </c>
+      <c r="E246" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="247" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B247" t="s">
+        <v>576</v>
+      </c>
+      <c r="C247" t="s">
+        <v>577</v>
+      </c>
+      <c r="D247" t="s">
+        <v>577</v>
+      </c>
+      <c r="E247" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="248" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B248" t="s">
+        <v>578</v>
+      </c>
+      <c r="C248" t="s">
+        <v>579</v>
+      </c>
+      <c r="D248" t="s">
+        <v>579</v>
+      </c>
+      <c r="E248" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="249" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B249" t="s">
+        <v>580</v>
+      </c>
+      <c r="C249" t="s">
+        <v>581</v>
+      </c>
+      <c r="D249" t="s">
+        <v>581</v>
+      </c>
+      <c r="E249" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="250" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B250" t="s">
+        <v>582</v>
+      </c>
+      <c r="C250" t="s">
+        <v>583</v>
+      </c>
+      <c r="D250" t="s">
+        <v>583</v>
+      </c>
+      <c r="E250" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="251" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B251" t="s">
+        <v>584</v>
+      </c>
+      <c r="C251" t="s">
+        <v>585</v>
+      </c>
+      <c r="D251" t="s">
+        <v>585</v>
+      </c>
+      <c r="E251" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="252" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B252" t="s">
+        <v>586</v>
+      </c>
+      <c r="C252" t="s">
+        <v>587</v>
+      </c>
+      <c r="D252" t="s">
+        <v>587</v>
+      </c>
+      <c r="E252" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="253" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B253" t="s">
+        <v>588</v>
+      </c>
+      <c r="C253" t="s">
+        <v>589</v>
+      </c>
+      <c r="D253" t="s">
+        <v>589</v>
+      </c>
+      <c r="E253" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="254" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B254" t="s">
+        <v>590</v>
+      </c>
+      <c r="C254" t="s">
+        <v>591</v>
+      </c>
+      <c r="D254" t="s">
+        <v>591</v>
+      </c>
+      <c r="E254" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="255" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B255" t="s">
+        <v>592</v>
+      </c>
+      <c r="C255" t="s">
+        <v>593</v>
+      </c>
+      <c r="D255" t="s">
+        <v>593</v>
+      </c>
+      <c r="E255" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="256" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B256" t="s">
+        <v>594</v>
+      </c>
+      <c r="C256" t="s">
+        <v>595</v>
+      </c>
+      <c r="D256" t="s">
+        <v>595</v>
+      </c>
+      <c r="E256" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="257" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B257" t="s">
+        <v>596</v>
+      </c>
+      <c r="C257" t="s">
+        <v>597</v>
+      </c>
+      <c r="D257" t="s">
+        <v>597</v>
+      </c>
+      <c r="E257" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="258" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B258" t="s">
+        <v>598</v>
+      </c>
+      <c r="C258" t="s">
+        <v>599</v>
+      </c>
+      <c r="D258" t="s">
+        <v>599</v>
+      </c>
+      <c r="E258" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="259" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B259" t="s">
+        <v>600</v>
+      </c>
+      <c r="C259" t="s">
+        <v>601</v>
+      </c>
+      <c r="D259" t="s">
+        <v>601</v>
+      </c>
+      <c r="E259" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="260" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B260" t="s">
+        <v>602</v>
+      </c>
+      <c r="C260" t="s">
+        <v>603</v>
+      </c>
+      <c r="D260" t="s">
+        <v>603</v>
+      </c>
+      <c r="E260" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="261" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B261" t="s">
+        <v>604</v>
+      </c>
+      <c r="C261" t="s">
+        <v>605</v>
+      </c>
+      <c r="D261" t="s">
+        <v>605</v>
+      </c>
+      <c r="E261" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="262" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B262" t="s">
+        <v>606</v>
+      </c>
+      <c r="C262" t="s">
+        <v>607</v>
+      </c>
+      <c r="D262" t="s">
+        <v>607</v>
+      </c>
+      <c r="E262" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="263" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B263" t="s">
+        <v>608</v>
+      </c>
+      <c r="C263" t="s">
+        <v>609</v>
+      </c>
+      <c r="D263" t="s">
+        <v>609</v>
+      </c>
+      <c r="E263" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="264" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B264" t="s">
+        <v>610</v>
+      </c>
+      <c r="C264" t="s">
+        <v>611</v>
+      </c>
+      <c r="D264" t="s">
+        <v>611</v>
+      </c>
+      <c r="E264" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="265" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B265" t="s">
+        <v>612</v>
+      </c>
+      <c r="C265" t="s">
+        <v>613</v>
+      </c>
+      <c r="D265" t="s">
+        <v>613</v>
+      </c>
+      <c r="E265" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="266" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B266" t="s">
+        <v>614</v>
+      </c>
+      <c r="C266" t="s">
+        <v>615</v>
+      </c>
+      <c r="D266" t="s">
+        <v>615</v>
+      </c>
+      <c r="E266" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="267" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B267" t="s">
+        <v>616</v>
+      </c>
+      <c r="C267" t="s">
+        <v>617</v>
+      </c>
+      <c r="D267" t="s">
+        <v>617</v>
+      </c>
+      <c r="E267" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="268" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B268" t="s">
+        <v>618</v>
+      </c>
+      <c r="C268" t="s">
+        <v>619</v>
+      </c>
+      <c r="D268" t="s">
+        <v>619</v>
+      </c>
+      <c r="E268" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="269" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B269" t="s">
+        <v>620</v>
+      </c>
+      <c r="C269" t="s">
+        <v>621</v>
+      </c>
+      <c r="D269" t="s">
+        <v>621</v>
+      </c>
+      <c r="E269" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="270" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B270" t="s">
+        <v>622</v>
+      </c>
+      <c r="C270" t="s">
+        <v>623</v>
+      </c>
+      <c r="D270" t="s">
+        <v>623</v>
+      </c>
+      <c r="E270" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="271" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B271" t="s">
+        <v>624</v>
+      </c>
+      <c r="C271" t="s">
+        <v>625</v>
+      </c>
+      <c r="D271" t="s">
+        <v>625</v>
+      </c>
+      <c r="E271" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="272" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B272" t="s">
+        <v>626</v>
+      </c>
+      <c r="C272" t="s">
+        <v>627</v>
+      </c>
+      <c r="D272" t="s">
+        <v>627</v>
+      </c>
+      <c r="E272" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="273" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B273" t="s">
+        <v>628</v>
+      </c>
+      <c r="C273" t="s">
+        <v>629</v>
+      </c>
+      <c r="D273" t="s">
+        <v>629</v>
+      </c>
+      <c r="E273" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="274" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B274" t="s">
+        <v>630</v>
+      </c>
+      <c r="C274" t="s">
+        <v>631</v>
+      </c>
+      <c r="D274" t="s">
+        <v>631</v>
+      </c>
+      <c r="E274" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="275" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B275" t="s">
+        <v>632</v>
+      </c>
+      <c r="C275" t="s">
+        <v>633</v>
+      </c>
+      <c r="D275" t="s">
+        <v>633</v>
+      </c>
+      <c r="E275" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="276" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B276" t="s">
+        <v>634</v>
+      </c>
+      <c r="C276" t="s">
+        <v>635</v>
+      </c>
+      <c r="D276" t="s">
+        <v>635</v>
+      </c>
+      <c r="E276" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="277" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B277" t="s">
+        <v>636</v>
+      </c>
+      <c r="C277" t="s">
+        <v>637</v>
+      </c>
+      <c r="D277" t="s">
+        <v>637</v>
+      </c>
+      <c r="E277" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="278" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B278" t="s">
+        <v>638</v>
+      </c>
+      <c r="C278" t="s">
+        <v>639</v>
+      </c>
+      <c r="D278" t="s">
+        <v>639</v>
+      </c>
+      <c r="E278" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="279" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B279" t="s">
+        <v>640</v>
+      </c>
+      <c r="C279" t="s">
+        <v>641</v>
+      </c>
+      <c r="D279" t="s">
+        <v>641</v>
+      </c>
+      <c r="E279" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="280" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B280" t="s">
+        <v>642</v>
+      </c>
+      <c r="C280" t="s">
+        <v>643</v>
+      </c>
+      <c r="D280" t="s">
+        <v>643</v>
+      </c>
+      <c r="E280" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="281" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B281" t="s">
+        <v>644</v>
+      </c>
+      <c r="C281" t="s">
+        <v>645</v>
+      </c>
+      <c r="D281" t="s">
+        <v>645</v>
+      </c>
+      <c r="E281" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="282" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B282" t="s">
+        <v>646</v>
+      </c>
+      <c r="C282" t="s">
+        <v>647</v>
+      </c>
+      <c r="D282" t="s">
+        <v>647</v>
+      </c>
+      <c r="E282" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="283" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B283" t="s">
+        <v>648</v>
+      </c>
+      <c r="C283" t="s">
+        <v>649</v>
+      </c>
+      <c r="D283" t="s">
+        <v>649</v>
+      </c>
+      <c r="E283" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="284" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B284" t="s">
+        <v>650</v>
+      </c>
+      <c r="C284" t="s">
+        <v>651</v>
+      </c>
+      <c r="D284" t="s">
+        <v>651</v>
+      </c>
+      <c r="E284" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="285" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B285" t="s">
+        <v>652</v>
+      </c>
+      <c r="C285" t="s">
+        <v>653</v>
+      </c>
+      <c r="D285" t="s">
+        <v>653</v>
+      </c>
+      <c r="E285" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="286" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B286" t="s">
+        <v>654</v>
+      </c>
+      <c r="C286" t="s">
+        <v>655</v>
+      </c>
+      <c r="D286" t="s">
+        <v>655</v>
+      </c>
+      <c r="E286" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="287" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B287" t="s">
+        <v>656</v>
+      </c>
+      <c r="C287" t="s">
+        <v>657</v>
+      </c>
+      <c r="D287" t="s">
+        <v>657</v>
+      </c>
+      <c r="E287" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="288" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B288" t="s">
+        <v>658</v>
+      </c>
+      <c r="C288" t="s">
+        <v>659</v>
+      </c>
+      <c r="D288" t="s">
+        <v>659</v>
+      </c>
+      <c r="E288" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="289" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B289" t="s">
+        <v>660</v>
+      </c>
+      <c r="C289" t="s">
+        <v>661</v>
+      </c>
+      <c r="D289" t="s">
+        <v>661</v>
+      </c>
+      <c r="E289" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="290" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B290" t="s">
+        <v>662</v>
+      </c>
+      <c r="C290" t="s">
+        <v>663</v>
+      </c>
+      <c r="D290" t="s">
+        <v>663</v>
+      </c>
+      <c r="E290" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="291" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B291" t="s">
+        <v>664</v>
+      </c>
+      <c r="C291" t="s">
+        <v>665</v>
+      </c>
+      <c r="D291" t="s">
+        <v>665</v>
+      </c>
+      <c r="E291" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="292" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B292" t="s">
+        <v>666</v>
+      </c>
+      <c r="C292" t="s">
+        <v>667</v>
+      </c>
+      <c r="D292" t="s">
+        <v>667</v>
+      </c>
+      <c r="E292" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="293" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B293" t="s">
+        <v>668</v>
+      </c>
+      <c r="C293" t="s">
+        <v>669</v>
+      </c>
+      <c r="D293" t="s">
+        <v>669</v>
+      </c>
+      <c r="E293" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="294" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B294" t="s">
+        <v>670</v>
+      </c>
+      <c r="C294" t="s">
+        <v>671</v>
+      </c>
+      <c r="D294" t="s">
+        <v>671</v>
+      </c>
+      <c r="E294" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="295" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B295" t="s">
+        <v>672</v>
+      </c>
+      <c r="C295" t="s">
+        <v>673</v>
+      </c>
+      <c r="D295" t="s">
+        <v>673</v>
+      </c>
+      <c r="E295" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="296" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B296" t="s">
+        <v>674</v>
+      </c>
+      <c r="C296" t="s">
+        <v>675</v>
+      </c>
+      <c r="D296" t="s">
+        <v>675</v>
+      </c>
+      <c r="E296" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="297" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B297" t="s">
+        <v>676</v>
+      </c>
+      <c r="C297" t="s">
+        <v>677</v>
+      </c>
+      <c r="D297" t="s">
+        <v>677</v>
+      </c>
+      <c r="E297" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="298" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B298" t="s">
+        <v>678</v>
+      </c>
+      <c r="C298" t="s">
+        <v>679</v>
+      </c>
+      <c r="D298" t="s">
+        <v>679</v>
+      </c>
+      <c r="E298" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71754C8A-E599-4286-919F-11B5789CC171}">
   <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34DC064-9DBC-455F-947D-388AD39D7DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD138997-FE09-4A2B-99CB-01A483120FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6BE46C4-ED8B-4DE6-A784-DD4A4ACCB706}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF74384C-4CFE-4176-9184-44D242A6AD66}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD138997-FE09-4A2B-99CB-01A483120FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F6AACA5-975B-4542-8BE9-434457BE50B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF74384C-4CFE-4176-9184-44D242A6AD66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E5921A-0141-4A09-8E03-E9C1D0C36F00}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F6AACA5-975B-4542-8BE9-434457BE50B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E36622E7-A28B-42D2-BC19-84BC42986F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E5921A-0141-4A09-8E03-E9C1D0C36F00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E76BC40-181F-4F85-85AF-CB34ABDEF851}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E36622E7-A28B-42D2-BC19-84BC42986F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9224B8DD-5415-4AE7-A2C2-6CF76D2D98E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E76BC40-181F-4F85-85AF-CB34ABDEF851}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C288D49D-DED4-490A-8C9B-5549EBFB5EA8}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9224B8DD-5415-4AE7-A2C2-6CF76D2D98E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13A5E855-24A4-45D0-B3FD-72B64D449F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C288D49D-DED4-490A-8C9B-5549EBFB5EA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4527BF12-B4D8-4E8D-819C-621210D40241}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13A5E855-24A4-45D0-B3FD-72B64D449F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F389BE0F-EA8C-4D9F-9853-C25F7DCB76CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4527BF12-B4D8-4E8D-819C-621210D40241}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80EE9D02-EAE5-481B-BEA4-079A43F46E3B}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F389BE0F-EA8C-4D9F-9853-C25F7DCB76CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03CC53EE-F32C-405F-B51C-8525F1511CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80EE9D02-EAE5-481B-BEA4-079A43F46E3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765917DC-E1CC-4337-8439-BFA7E3DA470B}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03CC53EE-F32C-405F-B51C-8525F1511CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B85A1A49-04E7-41C4-8450-E9067BB93FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765917DC-E1CC-4337-8439-BFA7E3DA470B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B23FD9C-CB3F-49CF-B2D6-48502CFD7BAE}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B85A1A49-04E7-41C4-8450-E9067BB93FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76AEBF88-4FAC-47A4-B85D-E1B20F0571B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B23FD9C-CB3F-49CF-B2D6-48502CFD7BAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6896D60D-876A-43B8-B72F-CEFA5C78D97C}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76AEBF88-4FAC-47A4-B85D-E1B20F0571B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2158312F-C3B3-4619-A1B2-81ED43DE5167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6896D60D-876A-43B8-B72F-CEFA5C78D97C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFED3F40-9674-482F-8900-92582B31B2E7}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2158312F-C3B3-4619-A1B2-81ED43DE5167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31EEE94-92C4-4EDB-9C99-F423EA0AA2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFED3F40-9674-482F-8900-92582B31B2E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1AAB61-83D5-437E-B685-3C137FF6CD65}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31EEE94-92C4-4EDB-9C99-F423EA0AA2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECEC1FFD-9D40-4A8D-BC66-D1F66BC5044A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1AAB61-83D5-437E-B685-3C137FF6CD65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7681B8-E128-463F-89FE-90B8D52C5CB3}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECEC1FFD-9D40-4A8D-BC66-D1F66BC5044A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE44B93F-A44F-485C-A8F4-9CA7B344ED6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7681B8-E128-463F-89FE-90B8D52C5CB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D868F1-B288-4A48-878B-4FB861899918}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE44B93F-A44F-485C-A8F4-9CA7B344ED6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FAF3EEA-A8C1-4D7F-BE5E-FA3EDCB0940C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D868F1-B288-4A48-878B-4FB861899918}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC8B08A-413B-4F49-AC50-37C05DCA9584}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FAF3EEA-A8C1-4D7F-BE5E-FA3EDCB0940C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EFF6C63-6144-4FD2-94F5-925D9A5EA906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC8B08A-413B-4F49-AC50-37C05DCA9584}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B523D178-9A8D-4020-8D93-07E8F3237E81}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EFF6C63-6144-4FD2-94F5-925D9A5EA906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9524F6D5-D334-46E4-9C35-DC3235C4CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B523D178-9A8D-4020-8D93-07E8F3237E81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220C9788-6DC3-4938-980F-08A14FA2DDE9}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9524F6D5-D334-46E4-9C35-DC3235C4CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84DDB6FC-277D-4E2D-AFF0-CD18A8EA902A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2915,7 +2915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220C9788-6DC3-4938-980F-08A14FA2DDE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6BD2A7E-4D35-4418-986F-91F08A39D4BB}">
   <dimension ref="B9:E298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84DDB6FC-277D-4E2D-AFF0-CD18A8EA902A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ABA0AC2-7DBF-4E03-BFFA-26B30BA4C4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="678">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -1622,12 +1622,6 @@
   </si>
   <si>
     <t>elc_spv_030</t>
-  </si>
-  <si>
-    <t>rez_spv_031</t>
-  </si>
-  <si>
-    <t>elc_spv_031</t>
   </si>
   <si>
     <t>rez_won_001</t>
@@ -2915,8 +2909,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6BD2A7E-4D35-4418-986F-91F08A39D4BB}">
-  <dimension ref="B9:E298"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2D81D7-BAC6-45AE-AF77-6B02CB59D0EC}">
+  <dimension ref="B9:E297"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -6953,20 +6947,6 @@
         <v>677</v>
       </c>
       <c r="E297" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B298" t="s">
-        <v>678</v>
-      </c>
-      <c r="C298" t="s">
-        <v>679</v>
-      </c>
-      <c r="D298" t="s">
-        <v>679</v>
-      </c>
-      <c r="E298" t="s">
         <v>105</v>
       </c>
     </row>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ABA0AC2-7DBF-4E03-BFFA-26B30BA4C4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE00B708-ECE7-4322-B8A6-032F3708F868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2909,7 +2909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2D81D7-BAC6-45AE-AF77-6B02CB59D0EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010EA616-D442-4756-B5B3-E4180AD7F7A1}">
   <dimension ref="B9:E297"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE00B708-ECE7-4322-B8A6-032F3708F868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83BEB3DC-ED77-4EEE-9F37-B42488D9C5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2909,7 +2909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{010EA616-D442-4756-B5B3-E4180AD7F7A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8C131D-7922-4392-B0D4-460BD1E615F9}">
   <dimension ref="B9:E297"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
